--- a/data/gravel/Turner Cyclosis Ti 2025.xlsx
+++ b/data/gravel/Turner Cyclosis Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA84253-D592-BB4C-B1DC-ECBFF6EA86D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7586BB-9576-3D4E-81D3-CA08551FA12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1540" yWindow="500" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27480" yWindow="-18660" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="99">
   <si>
     <t>brand</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>drop bar</t>
+  </si>
+  <si>
+    <t>https://turnerbikes.com/cdn/shop/files/CYCLOSIS-side-3.jpg?v=1759532926&amp;width=1500</t>
   </si>
 </sst>
 </file>
@@ -756,6 +759,11 @@
         <v>93</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Turner Cyclosis Ti 2025.xlsx
+++ b/data/gravel/Turner Cyclosis Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7586BB-9576-3D4E-81D3-CA08551FA12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE41295A-51CF-DA40-803E-A6DE3B37F10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27480" yWindow="-18660" windowWidth="27260" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="101">
   <si>
     <t>brand</t>
   </si>
@@ -272,9 +272,6 @@
     <t>threaded</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>sm</t>
   </si>
   <si>
@@ -330,6 +327,15 @@
   </si>
   <si>
     <t>https://turnerbikes.com/cdn/shop/files/CYCLOSIS-side-3.jpg?v=1759532926&amp;width=1500</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Murrieta, California, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -712,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -724,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -732,7 +738,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -756,12 +762,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -769,7 +775,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -780,16 +786,16 @@
         <v>77</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="F8" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>83</v>
       </c>
       <c r="G8" s="5"/>
     </row>
@@ -798,7 +804,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" s="9">
         <v>540</v>
@@ -818,7 +824,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" s="9">
         <v>430</v>
@@ -839,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" s="9">
         <v>74.5</v>
@@ -860,7 +866,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C12" s="9">
         <v>135</v>
@@ -881,7 +887,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C13" s="9">
         <v>70</v>
@@ -902,7 +908,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C14" s="9">
         <v>75</v>
@@ -923,7 +929,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C15" s="9">
         <v>430</v>
@@ -1249,7 +1255,7 @@
         <v>66</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -1262,7 +1268,7 @@
         <v>67</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -1282,7 +1288,7 @@
         <v>31</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
@@ -1500,7 +1506,15 @@
         <v>65</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Turner Cyclosis Ti 2025.xlsx
+++ b/data/gravel/Turner Cyclosis Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE41295A-51CF-DA40-803E-A6DE3B37F10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A455ACD-4BBD-8E48-849B-10BC91184E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -336,6 +336,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -718,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1358,162 +1376,192 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="1">
-        <v>27.2</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B60" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="1">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B66" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B67" s="1">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B71" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B72" s="1">
-        <v>2990</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="B73" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" s="1">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>99</v>
       </c>
     </row>
